--- a/backend/downloads/국토계획_국토지표의 진전 (1981 ~ 2024).xlsx
+++ b/backend/downloads/국토계획_국토지표의 진전 (1981 ~ 2024).xlsx
@@ -160,7 +160,7 @@
     <row r="2" customHeight="true" ht="25.0">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>다운로드 시간 : 2025-10-17   00:07</t>
+          <t>다운로드 시간 : 2025-10-17   08:20</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
